--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X109"/>
+  <dimension ref="A1:X110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8949,19 +8949,19 @@
         <v>145.462</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>0.2</v>
+        <v>0.201834</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>3.26</v>
+        <v>3.261942</v>
       </c>
       <c r="F109" s="10" t="n">
         <v>146.22885</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>0.16</v>
+        <v>0.156683</v>
       </c>
       <c r="H109" s="11" t="n">
-        <v>3.88</v>
+        <v>3.883834</v>
       </c>
       <c r="I109" s="11" t="n">
         <v>0.11</v>
@@ -9015,6 +9015,86 @@
         </is>
       </c>
       <c r="X109" s="13" t="inlineStr">
+        <is>
+          <t>7 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="F110" s="6" t="n"/>
+      <c r="G110" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I110" s="7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J110" s="7" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="K110" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L110" s="7" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M110" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N110" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O110" s="7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P110" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q110" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="R110" s="7" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="S110" s="8" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="T110" s="8" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="U110" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V110" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W110" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X110" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -9029,14 +9029,18 @@
       <c r="B110" s="5" t="n">
         <v>46266</v>
       </c>
-      <c r="C110" s="6" t="n"/>
+      <c r="C110" s="6" t="n">
+        <v>146.075</v>
+      </c>
       <c r="D110" s="7" t="n">
         <v>0.42</v>
       </c>
       <c r="E110" s="7" t="n">
         <v>3.45</v>
       </c>
-      <c r="F110" s="6" t="n"/>
+      <c r="F110" s="6" t="n">
+        <v>146.521241</v>
+      </c>
       <c r="G110" s="7" t="n">
         <v>0.2</v>
       </c>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -526,7 +526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf · Fecha de publicación: 7 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf · Fecha de publicación: 8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -723,12 +723,12 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X6" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="W7" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X7" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X8" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="W9" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X9" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X10" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="W11" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X11" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X12" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="W13" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X13" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X14" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="W15" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X15" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X16" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="W17" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X17" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X18" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="W19" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X19" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X20" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="W21" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X21" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X22" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="W23" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X23" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X24" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="W25" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X25" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X26" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="W27" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X27" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X28" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="W29" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X29" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X30" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="W31" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X31" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X32" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="W33" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X33" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2963,12 +2963,12 @@
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X34" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="W35" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X35" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X36" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="W37" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X37" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X38" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="W39" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X39" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X40" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3523,12 +3523,12 @@
       </c>
       <c r="W41" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X41" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3603,12 +3603,12 @@
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X42" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="W43" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X43" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X44" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3843,12 +3843,12 @@
       </c>
       <c r="W45" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X45" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X46" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4003,12 +4003,12 @@
       </c>
       <c r="W47" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X47" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X48" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="W49" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X49" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X50" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="W51" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X51" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4403,12 +4403,12 @@
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X52" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="W53" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X53" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4563,12 @@
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X54" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="W55" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X55" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4723,12 +4723,12 @@
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X56" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4803,12 @@
       </c>
       <c r="W57" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X57" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X58" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="W59" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X59" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X60" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="W61" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X61" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5203,12 +5203,12 @@
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X62" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="W63" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X63" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5363,12 +5363,12 @@
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X64" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5443,12 +5443,12 @@
       </c>
       <c r="W65" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X65" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="W66" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X66" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="W67" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X67" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5683,12 +5683,12 @@
       </c>
       <c r="W68" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X68" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="W69" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X69" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="W70" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X70" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5923,12 +5923,12 @@
       </c>
       <c r="W71" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X71" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="W72" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X72" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6083,12 +6083,12 @@
       </c>
       <c r="W73" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X73" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="W74" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X74" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6243,12 +6243,12 @@
       </c>
       <c r="W75" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X75" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="W76" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X76" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6403,12 @@
       </c>
       <c r="W77" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X77" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6483,12 +6483,12 @@
       </c>
       <c r="W78" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X78" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6563,12 +6563,12 @@
       </c>
       <c r="W79" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X79" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6643,12 @@
       </c>
       <c r="W80" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X80" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6723,12 @@
       </c>
       <c r="W81" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X81" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="W82" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X82" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="W83" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X83" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6963,12 +6963,12 @@
       </c>
       <c r="W84" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X84" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7043,12 +7043,12 @@
       </c>
       <c r="W85" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X85" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="W86" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X86" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="W87" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X87" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7283,12 @@
       </c>
       <c r="W88" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X88" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7363,12 +7363,12 @@
       </c>
       <c r="W89" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X89" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="W90" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X90" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="W91" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X91" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="W92" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X92" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7683,12 +7683,12 @@
       </c>
       <c r="W93" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X93" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="W94" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X94" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7843,12 +7843,12 @@
       </c>
       <c r="W95" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X95" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="W96" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X96" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8003,12 @@
       </c>
       <c r="W97" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X97" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8025,19 +8025,19 @@
         <v>141.197</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>0.234264</v>
+        <v>0.23</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>3.760288</v>
+        <v>3.76</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>141.227101</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0.330494</v>
+        <v>0.33</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>4.277929</v>
+        <v>4.28</v>
       </c>
       <c r="I98" s="7" t="n">
         <v>0.34</v>
@@ -8087,12 +8087,12 @@
       </c>
       <c r="W98" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X98" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8109,19 +8109,19 @@
         <v>141.708</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>0.361906</v>
+        <v>0.36</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>3.566521</v>
+        <v>3.57</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>141.630371</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0.285547</v>
+        <v>0.29</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>4.28375</v>
+        <v>4.28</v>
       </c>
       <c r="I99" s="11" t="n">
         <v>0.17</v>
@@ -8171,12 +8171,12 @@
       </c>
       <c r="W99" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X99" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8193,19 +8193,19 @@
         <v>142.645</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>0.661219</v>
+        <v>0.66</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>3.799191</v>
+        <v>3.8</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>141.895672</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>0.187319</v>
+        <v>0.19</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>4.430588</v>
+        <v>4.43</v>
       </c>
       <c r="I100" s="7" t="n">
         <v>-0.03</v>
@@ -8255,12 +8255,12 @@
       </c>
       <c r="W100" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X100" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8277,19 +8277,19 @@
         <v>143.042</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>0.278313</v>
+        <v>0.28</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>3.691944</v>
+        <v>3.69</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>142.474483</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>0.407913</v>
+        <v>0.41</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>4.325358</v>
+        <v>4.33</v>
       </c>
       <c r="I101" s="11" t="n">
         <v>0.33</v>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="W101" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X101" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8361,19 +8361,19 @@
         <v>143.588</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>0.381706</v>
+        <v>0.38</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>3.791301</v>
+        <v>3.79</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>143.331326</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>0.601401</v>
+        <v>0.6</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>4.51917</v>
+        <v>4.52</v>
       </c>
       <c r="I102" s="7" t="n">
         <v>0.92</v>
@@ -8423,12 +8423,12 @@
       </c>
       <c r="W102" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X102" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8445,19 +8445,19 @@
         <v>144.307</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>0.500738</v>
+        <v>0.5</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>4.023038</v>
+        <v>4.02</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>143.98976</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>0.459379</v>
+        <v>0.46</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>4.497411</v>
+        <v>4.5</v>
       </c>
       <c r="I103" s="11" t="n">
         <v>0.39</v>
@@ -8507,12 +8507,12 @@
       </c>
       <c r="W103" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X103" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8529,19 +8529,19 @@
         <v>145.544</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>0.8572</v>
+        <v>0.86</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>4.586774</v>
+        <v>4.59</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>144.543429</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>0.384519</v>
+        <v>0.38</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>4.449385</v>
+        <v>4.45</v>
       </c>
       <c r="I104" s="7" t="n">
         <v>0.29</v>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="W104" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X104" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8613,19 +8613,19 @@
         <v>145.831</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>0.197191</v>
+        <v>0.2</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>4.448503</v>
+        <v>4.45</v>
       </c>
       <c r="F105" s="10" t="n">
         <v>144.991329</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.309872</v>
+        <v>0.31</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>4.261182</v>
+        <v>4.26</v>
       </c>
       <c r="I105" s="11" t="n">
         <v>0.31</v>
@@ -8675,12 +8675,12 @@
       </c>
       <c r="W105" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X105" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8697,19 +8697,19 @@
         <v>145.527</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>-0.20846</v>
+        <v>-0.21</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>3.938948</v>
+        <v>3.94</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>145.315299</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.223441</v>
+        <v>0.22</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>4.186559</v>
+        <v>4.19</v>
       </c>
       <c r="I106" s="7" t="n">
         <v>0.16</v>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="W106" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X106" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8781,19 +8781,19 @@
         <v>145.131</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>-0.272114</v>
+        <v>-0.27</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>3.365977</v>
+        <v>3.37</v>
       </c>
       <c r="F107" s="10" t="n">
         <v>145.671279</v>
       </c>
       <c r="G107" s="11" t="n">
-        <v>0.24497</v>
+        <v>0.24</v>
       </c>
       <c r="H107" s="11" t="n">
-        <v>4.03192</v>
+        <v>4.03</v>
       </c>
       <c r="I107" s="11" t="n">
         <v>0.18</v>
@@ -8843,12 +8843,12 @@
       </c>
       <c r="W107" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X107" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8865,19 +8865,19 @@
         <v>145.169</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>0.026183</v>
+        <v>0.03</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>3.11763</v>
+        <v>3.12</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>146.000093</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>0.225723</v>
+        <v>0.23</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>3.948334</v>
+        <v>3.95</v>
       </c>
       <c r="I108" s="7" t="n">
         <v>0.19</v>
@@ -8927,12 +8927,12 @@
       </c>
       <c r="W108" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X108" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8949,19 +8949,19 @@
         <v>145.462</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>0.201834</v>
+        <v>0.2</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>3.261942</v>
+        <v>3.26</v>
       </c>
       <c r="F109" s="10" t="n">
         <v>146.22885</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>0.156683</v>
+        <v>0.16</v>
       </c>
       <c r="H109" s="11" t="n">
-        <v>3.883834</v>
+        <v>3.88</v>
       </c>
       <c r="I109" s="11" t="n">
         <v>0.11</v>
@@ -9011,12 +9011,12 @@
       </c>
       <c r="W109" s="13" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X109" s="13" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9095,12 +9095,12 @@
       </c>
       <c r="W110" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_10.pdf</t>
         </is>
       </c>
       <c r="X110" s="9" t="inlineStr">
         <is>
-          <t>7 de agosto de 2026</t>
+          <t>8 de octubre de 2026</t>
         </is>
       </c>
     </row>
